--- a/Datos ESPARTACO/Parámetros para análisis de Antares/comparación chi cuadrado espectros del 2018.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/comparación chi cuadrado espectros del 2018.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7496</v>
+        <v>0.742</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7523</v>
+        <v>0.7897</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7527</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="3">
@@ -473,10 +473,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.387</v>
+        <v>0.3645</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3902</v>
+        <v>0.3685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4453</v>
+        <v>0.4388</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4533</v>
+        <v>0.4388</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4547</v>
+        <v>0.4388</v>
       </c>
     </row>
     <row r="5">
@@ -507,13 +507,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3832</v>
+        <v>0.3743</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3839</v>
+        <v>0.3751</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3843</v>
+        <v>0.3755</v>
       </c>
     </row>
     <row r="6">
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4572</v>
+        <v>0.4465</v>
       </c>
       <c r="C6" t="n">
-        <v>0.459</v>
+        <v>0.4823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -541,13 +541,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5188</v>
+        <v>0.5046</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5212</v>
+        <v>0.5064</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5205</v>
+        <v>0.5076000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -557,13 +557,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.4033</v>
+        <v>0.3995</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4051</v>
+        <v>0.4002</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4054</v>
+        <v>0.4004</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9621</v>
+        <v>0.9483</v>
       </c>
       <c r="C9" t="n">
-        <v>0.964</v>
+        <v>0.9516</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9633</v>
+        <v>0.9527</v>
       </c>
     </row>
     <row r="10">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9384</v>
+        <v>0.9271</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9442</v>
+        <v>0.928</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9436</v>
+        <v>0.9286</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/comparación chi cuadrado espectros del 2018.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/comparación chi cuadrado espectros del 2018.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>χ² (Centro Libre)</t>
+          <t>χ² (Hα)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>χ² (Vis)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>χ² (IR)</t>
+          <t>χ² (SN)</t>
         </is>
       </c>
     </row>
@@ -457,13 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.742</v>
+        <v>0.7557</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7897</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.742</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="3">
@@ -473,12 +465,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3645</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.3685</v>
-      </c>
-      <c r="D3" t="inlineStr">
+        <v>0.3863</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>No existe</t>
         </is>
@@ -491,13 +480,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4388</v>
+        <v>0.4816</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4388</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.4388</v>
+        <v>0.4508</v>
       </c>
     </row>
     <row r="5">
@@ -507,13 +493,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3743</v>
+        <v>0.4017</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3751</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.3755</v>
+        <v>0.4101</v>
       </c>
     </row>
     <row r="6">
@@ -523,12 +506,9 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4465</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.4823</v>
-      </c>
-      <c r="D6" t="inlineStr">
+        <v>0.4674</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>No existe</t>
         </is>
@@ -541,13 +521,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5046</v>
+        <v>0.5274</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5064</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.5076000000000001</v>
+        <v>0.5415</v>
       </c>
     </row>
     <row r="8">
@@ -557,13 +534,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3995</v>
+        <v>0.415</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4002</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4004</v>
+        <v>0.4208</v>
       </c>
     </row>
     <row r="9">
@@ -573,13 +547,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9483</v>
+        <v>0.9725</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9516</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.9527</v>
+        <v>0.985</v>
       </c>
     </row>
     <row r="10">
@@ -589,13 +560,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9271</v>
+        <v>0.9368</v>
       </c>
       <c r="C10" t="n">
-        <v>0.928</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.9286</v>
+        <v>0.9455</v>
       </c>
     </row>
   </sheetData>

--- a/Datos ESPARTACO/Parámetros para análisis de Antares/comparación chi cuadrado espectros del 2018.xlsx
+++ b/Datos ESPARTACO/Parámetros para análisis de Antares/comparación chi cuadrado espectros del 2018.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>χ²</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -442,6 +442,16 @@
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>χ² (SN)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Incertidumbre v Hα [km/s]</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Incertidumbre v SN [km/s]</t>
         </is>
       </c>
     </row>
@@ -457,6 +467,12 @@
       <c r="C2" t="n">
         <v>0.763</v>
       </c>
+      <c r="D2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -472,6 +488,14 @@
           <t>No existe</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>No existe</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -485,6 +509,12 @@
       <c r="C4" t="n">
         <v>0.4508</v>
       </c>
+      <c r="D4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -498,6 +528,12 @@
       <c r="C5" t="n">
         <v>0.4101</v>
       </c>
+      <c r="D5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -513,6 +549,14 @@
           <t>No existe</t>
         </is>
       </c>
+      <c r="D6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>No existe</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -526,6 +570,12 @@
       <c r="C7" t="n">
         <v>0.5415</v>
       </c>
+      <c r="D7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -539,6 +589,12 @@
       <c r="C8" t="n">
         <v>0.4208</v>
       </c>
+      <c r="D8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -552,6 +608,12 @@
       <c r="C9" t="n">
         <v>0.985</v>
       </c>
+      <c r="D9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -564,6 +626,12 @@
       </c>
       <c r="C10" t="n">
         <v>0.9455</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.09</v>
       </c>
     </row>
   </sheetData>
